--- a/results/job_matches_2026-10-03.xlsx
+++ b/results/job_matches_2026-10-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,52 +596,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Managing Consultant, Palantir Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712c0b25aa3285b3</t>
+          <t>https://www.indeed.com/viewjob?jk=4c403fce849834db</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Managing Consultant, Palantir Data &amp; AI Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,14 +659,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c403fce849834db</t>
+          <t>https://www.indeed.com/viewjob?jk=42cd837866eddbf4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -676,15 +676,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>Miami Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,14 +694,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42cd837866eddbf4</t>
+          <t>https://www.indeed.com/viewjob?jk=ef02d35010b82b3e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Data Context Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Miami Beach, FL, US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -719,34 +719,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef02d35010b82b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=2977ae9b1f2b1c97</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Context Engineer</t>
+          <t>DevOps Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ralph Lauren</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,77 +754,77 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2977ae9b1f2b1c97</t>
+          <t>https://www.indeed.com/viewjob?jk=0965aea3b361ff0b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Developer</t>
+          <t>Senior Databricks Migration Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ralph Lauren</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0965aea3b361ff0b</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd5a045970f362d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Databricks Migration Engineer</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>US Neuro LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,59 +834,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd5a045970f362d</t>
+          <t>https://www.indeed.com/viewjob?jk=5acff10101632d23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>TGS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c381b09f7b36b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6251b84b65aed773</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - AWS, Databricks, Python</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,17 +894,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45753ce4c6ce5c87</t>
+          <t>https://www.indeed.com/viewjob?jk=54895b1eb093622c</t>
         </is>
       </c>
     </row>
@@ -981,17 +981,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer | Talent Community</t>
+          <t>Senior Full Stack Developer - Java, Angular</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,17 +999,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, ECS, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6682604b8f254c7</t>
+          <t>https://www.indeed.com/viewjob?jk=f75183eedc15fcaa</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Backend Cloud Engineer</t>
+          <t>CX Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1485,73 +1485,73 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, IAM, RDS, Azure, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8672fb0f9146fe17</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c2fd229b2485eb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Engineer-API -Global Industrial</t>
+          <t>Sr Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e80d57311917aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=3a085e8b62912626</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CX Machine Learning Engineer</t>
+          <t>Simulation Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c2fd229b2485eb</t>
+          <t>https://www.indeed.com/viewjob?jk=b856865fd8381428</t>
         </is>
       </c>
     </row>
@@ -1611,17 +1611,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (AWS), AI Infrastructure - Evinova</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Vertex AI, Scala, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc9132b08227ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c0b1ce938721b8</t>
         </is>
       </c>
     </row>
@@ -1681,17 +1681,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Architect - Indiana</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,32 +1709,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9963d3eedaca5e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=607e2aeb25bf6f87</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Workday Solution Architect - Healthcare Domain</t>
+          <t>Software Engineer (Java and Big Data)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ITiNovate</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,32 +1744,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c679d851f8a17b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9feb9788d5ad86</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Software Engineer (Java/Big Data)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,102 +1779,102 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e725f6b9e8655bb</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8a623c5a6c2d7b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Athena, RDS, Azure, Data Factory, Snowflake, SQL Server, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607e2aeb25bf6f87</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa8113d5aa47de0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FBS Senior Data Engineer (SnowFlake)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Farmers Insurance Group</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740eac621cae0ece</t>
+          <t>https://www.indeed.com/viewjob?jk=80ca86983beb5881</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - ED&amp;A - Global Industrial</t>
+          <t>Data Analytics Specialist Sr</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Lutz, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, BigQuery, Cloud Storage, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Cloud Storage, Snowflake, ETL, Power BI, AKS, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,32 +1884,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a687a0075d547d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d56b5bcf4b7f491</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer (Java and Big Data)</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,32 +1919,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9feb9788d5ad86</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0579d402aad195</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer (Java/Big Data)</t>
+          <t>Senior Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,102 +1954,102 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8a623c5a6c2d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0cc391e05fe7617</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, Data Factory, Snowflake, SQL Server, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa8113d5aa47de0</t>
+          <t>https://www.indeed.com/viewjob?jk=26f314384566e0df</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ChenMed</t>
+          <t>Capitol Tech Solutions Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e9d9a6218bf629</t>
+          <t>https://www.indeed.com/viewjob?jk=89beb9e611e7e10d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Blood Cancer United</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,32 +2059,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ca86983beb5881</t>
+          <t>https://www.indeed.com/viewjob?jk=36d95a91a9b838e2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Analytics Specialist Sr</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>World View</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lutz, FL, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Cloud Storage, Snowflake, ETL, Power BI, AKS, Git</t>
+          <t>AWS, RDS, Azure, YARN, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,24 +2094,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d56b5bcf4b7f491</t>
+          <t>https://www.indeed.com/viewjob?jk=17fce9c056aead2f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Engineer</t>
+          <t>Senior Backend Developer (AI, Python)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cc391e05fe7617</t>
+          <t>https://www.indeed.com/viewjob?jk=9542b5c0a62999f1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Full-stack Engineer 4, Cyber Identity Security</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,24 +2164,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26f314384566e0df</t>
+          <t>https://www.indeed.com/viewjob?jk=5c73541ffb28ff13</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4 (Java, Spring Boot, Python, CI/CD)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capitol Tech Solutions Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,24 +2199,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89beb9e611e7e10d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd55268246c76b99</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Blood Cancer United</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,67 +2234,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d95a91a9b838e2</t>
+          <t>https://www.indeed.com/viewjob?jk=5a68879b2db22f8d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; BI/Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Advancio</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Downey, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30859e3f8aec8e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b9acf387c2adab</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Application Development</t>
+          <t>Senior Full-Stack Qlik Sense Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker</t>
+          <t>RDS, Hive, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,32 +2304,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60692df11bdfda4</t>
+          <t>https://www.indeed.com/viewjob?jk=84a405ff1d454ffa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior QA Infrastructure Engineer</t>
+          <t>Marketing Data Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ONENERGY</t>
+          <t>Hoover Institution, Stanford University</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Stanford, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, PostgreSQL, MySQL, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>EMR, RDS, Medallion Architecture, BigQuery, ELT, dbt, Power BI, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,32 +2339,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b5c19120976885</t>
+          <t>https://www.indeed.com/viewjob?jk=e021664b78377650</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Backend Developer (AI, Python)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Trisura</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,32 +2374,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9542b5c0a62999f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fb367a6965b10d25</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>World View</t>
+          <t>Trisura Guarantee Insurance Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,32 +2409,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17fce9c056aead2f</t>
+          <t>https://www.indeed.com/viewjob?jk=b91959ca412b5c96</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Kubernetes Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>API Gateway, RDS, Vertex AI, Scala, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2444,24 +2444,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b862a52465289faa</t>
+          <t>https://www.indeed.com/viewjob?jk=5de56e58a17ea8ab</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer Stf - E4</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,29 +2469,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, Python</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b9acf387c2adab</t>
+          <t>https://www.indeed.com/viewjob?jk=5d07b7c7063ad320</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Qlik Sense Engineer</t>
+          <t>Site Reliability Engineer (IT Infrastructure Engineer 2) - Provisional</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>City University of New York</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2504,34 +2504,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Hive, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, Git, Python</t>
+          <t>RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a405ff1d454ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=c2241815f02a7263</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Junior Azure Data Engineer - UniFirst</t>
+          <t>Engineer, IT AI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2539,29 +2539,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, Azure, Scala, Oracle, Jenkins, Maven, Docker, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44239a8e09ed622</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4b0626ba24d7d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IT Data Engineer II</t>
+          <t>​​Sr. Business Intelligence Developer​</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GCI</t>
+          <t>KLDiscovery</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2574,34 +2574,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, REST API integration, Power BI, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f42d08c79858e06</t>
+          <t>https://www.indeed.com/viewjob?jk=8e982a157a7d0ccb</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Marketing Data Analyst</t>
+          <t>Sr. Salesforce Analyst</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hoover Institution, Stanford University</t>
+          <t>Marvin</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Stanford, CA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>EMR, RDS, Medallion Architecture, BigQuery, ELT, dbt, Power BI, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, BigQuery, Dataflow, Scala, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,24 +2619,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e021664b78377650</t>
+          <t>https://www.indeed.com/viewjob?jk=b658acd57044b855</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Trisura</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,24 +2654,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb367a6965b10d25</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f5b97a41606b41</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer - Level 2 - Mobility</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Trisura Guarantee Insurance Company</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2689,24 +2689,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b91959ca412b5c96</t>
+          <t>https://www.indeed.com/viewjob?jk=4236b2cd8b3fe758</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Kubernetes Platform Engineer</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2714,34 +2714,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Vertex AI, Scala, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5de56e58a17ea8ab</t>
+          <t>https://www.indeed.com/viewjob?jk=32cddfff9e812a7c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer Stf - E4</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2749,34 +2749,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d07b7c7063ad320</t>
+          <t>https://www.indeed.com/viewjob?jk=387517c4b6923e55</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Salesforce Analyst</t>
+          <t>Data Engineer III (US)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Marvin</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Dataflow, Scala, ETL, dbt, Power BI, Tableau</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Oracle, SQL Server, Data Modeling, ETL, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2794,24 +2794,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b658acd57044b855</t>
+          <t>https://www.indeed.com/viewjob?jk=99283d35a189051e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>​​Sr. Business Intelligence Developer​</t>
+          <t>Junior Data and AI-ML Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>KLDiscovery</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, REST API integration, Power BI, Azure DevOps, Python</t>
+          <t>AWS, Databricks, Spark, Scala, ETL, ELT, dbt, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2828,216 +2828,6 @@
         </is>
       </c>
       <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e982a157a7d0ccb</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Data Engineer III (US)</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Mount Laurel, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Oracle, SQL Server, Data Modeling, ETL, Python</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99283d35a189051e</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>C.H. Robinson</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f5b97a41606b41</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Software Engineer - Level 2 - Mobility</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Cintas</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Mason, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4236b2cd8b3fe758</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Engineer III</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=32cddfff9e812a7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Engineer III</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=387517c4b6923e55</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Junior Data and AI-ML Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Lenovo</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Morrisville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Spark, Scala, ETL, ELT, dbt, Power BI, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=29f22521f3c1e203</t>
         </is>

--- a/results/job_matches_2026-10-03.xlsx
+++ b/results/job_matches_2026-10-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1191,17 +1191,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Database and Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Builders</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New Bedford, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Scala, Databricks Lakehouse, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,32 +1219,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2689f756f071cb85</t>
+          <t>https://www.indeed.com/viewjob?jk=179abbf1882c12d5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Database and Platform Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Builders</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ocala, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Scala, Databricks Lakehouse, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,32 +1254,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179abbf1882c12d5</t>
+          <t>https://www.indeed.com/viewjob?jk=33242063b9c39c59</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer II - Zelle</t>
+          <t>Senior Data Engineer - Indiana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de6c389d68d3fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=580c86eee0ba70b4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ocala, FL, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,34 +1314,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33242063b9c39c59</t>
+          <t>https://www.indeed.com/viewjob?jk=4788a8d5c641974d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI Engineer Associate Consultant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ocala, FL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,32 +1359,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6937b97dd55bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=fb36d41ad52a06bd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Indiana</t>
+          <t>CX Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,67 +1394,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580c86eee0ba70b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c2fd229b2485eb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4788a8d5c641974d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a085e8b62912626</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Engineer Associate Consultant</t>
+          <t>Simulation Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,24 +1464,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb36d41ad52a06bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b856865fd8381428</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CX Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Sentinel Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,24 +1499,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c2fd229b2485eb</t>
+          <t>https://www.indeed.com/viewjob?jk=e995e33ef6181c97</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - Databricks</t>
+          <t>Senior Guidewire Engineer (PolicyCenter)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,24 +1524,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Cloud Storage, Spark, Scala</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a085e8b62912626</t>
+          <t>https://www.indeed.com/viewjob?jk=09a5908bdb474bc4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Simulation Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,24 +1569,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b856865fd8381428</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c0b1ce938721b8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sentinel Group</t>
+          <t>GA Telesis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,24 +1604,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e995e33ef6181c97</t>
+          <t>https://www.indeed.com/viewjob?jk=dfd341b35c80136f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,32 +1639,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c0b1ce938721b8</t>
+          <t>https://www.indeed.com/viewjob?jk=607e2aeb25bf6f87</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer (Java and Big Data)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GA Telesis</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Oracle</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,32 +1674,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfd341b35c80136f</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9feb9788d5ad86</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Software Engineer (Java/Big Data)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,24 +1709,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607e2aeb25bf6f87</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8a623c5a6c2d7b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer (Java and Big Data)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,34 +1734,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
+          <t>AWS, Athena, RDS, Azure, Data Factory, Snowflake, SQL Server, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9feb9788d5ad86</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa8113d5aa47de0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer (Java/Big Data)</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,34 +1769,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8a623c5a6c2d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c7e630377051dd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,34 +1804,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, Data Factory, Snowflake, SQL Server, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa8113d5aa47de0</t>
+          <t>https://www.indeed.com/viewjob?jk=80ca86983beb5881</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Analytics Specialist Sr</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Lutz, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Cloud Storage, Snowflake, ETL, Power BI, AKS, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,32 +1849,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ca86983beb5881</t>
+          <t>https://www.indeed.com/viewjob?jk=6d56b5bcf4b7f491</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Analytics Specialist Sr</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lutz, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Cloud Storage, Snowflake, ETL, Power BI, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,24 +1884,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d56b5bcf4b7f491</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0579d402aad195</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Senior Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,24 +1919,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0579d402aad195</t>
+          <t>https://www.indeed.com/viewjob?jk=e0cc391e05fe7617</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Engineer</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,24 +1954,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cc391e05fe7617</t>
+          <t>https://www.indeed.com/viewjob?jk=26f314384566e0df</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capitol Tech Solutions Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26f314384566e0df</t>
+          <t>https://www.indeed.com/viewjob?jk=89beb9e611e7e10d</t>
         </is>
       </c>
     </row>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capitol Tech Solutions Inc</t>
+          <t>Blood Cancer United</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,24 +2024,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89beb9e611e7e10d</t>
+          <t>https://www.indeed.com/viewjob?jk=36d95a91a9b838e2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blood Cancer United</t>
+          <t>World View</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, YARN, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d95a91a9b838e2</t>
+          <t>https://www.indeed.com/viewjob?jk=17fce9c056aead2f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-stack Engineer 4, Cyber Identity Security</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>World View</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,24 +2094,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17fce9c056aead2f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c73541ffb28ff13</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Backend Developer (AI, Python)</t>
+          <t>Full-stack Engineer 4 (Java, Spring Boot, Python, CI/CD)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,14 +2129,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9542b5c0a62999f1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd55268246c76b99</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Cyber Identity Security</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2164,32 +2164,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c73541ffb28ff13</t>
+          <t>https://www.indeed.com/viewjob?jk=5a68879b2db22f8d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Spring Boot, Python, CI/CD)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,19 +2199,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd55268246c76b99</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b9acf387c2adab</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Senior Full-Stack Qlik Sense Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2220,11 +2220,11 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Hive, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,24 +2234,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a68879b2db22f8d</t>
+          <t>https://www.indeed.com/viewjob?jk=84a405ff1d454ffa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Associate – Palantir Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2259,34 +2259,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b9acf387c2adab</t>
+          <t>https://www.indeed.com/viewjob?jk=f170b110a592bbc2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Qlik Sense Engineer</t>
+          <t>Marketing Data Analyst</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Hoover Institution, Stanford University</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Stanford, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Hive, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, Git, Python</t>
+          <t>EMR, RDS, Medallion Architecture, BigQuery, ELT, dbt, Power BI, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,24 +2304,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a405ff1d454ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=e021664b78377650</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Marketing Data Analyst</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hoover Institution, Stanford University</t>
+          <t>Trisura</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Stanford, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>EMR, RDS, Medallion Architecture, BigQuery, ELT, dbt, Power BI, Tableau, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e021664b78377650</t>
+          <t>https://www.indeed.com/viewjob?jk=fb367a6965b10d25</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Trisura</t>
+          <t>Trisura Guarantee Insurance Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2374,24 +2374,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb367a6965b10d25</t>
+          <t>https://www.indeed.com/viewjob?jk=b91959ca412b5c96</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Sr Kubernetes Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Trisura Guarantee Insurance Company</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>API Gateway, RDS, Vertex AI, Scala, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,24 +2409,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b91959ca412b5c96</t>
+          <t>https://www.indeed.com/viewjob?jk=5de56e58a17ea8ab</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Kubernetes Platform Engineer</t>
+          <t>Data Engineer Stf - E4</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,34 +2434,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Vertex AI, Scala, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5de56e58a17ea8ab</t>
+          <t>https://www.indeed.com/viewjob?jk=5d07b7c7063ad320</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer Stf - E4</t>
+          <t>Site Reliability Engineer (IT Infrastructure Engineer 2) - Provisional</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>City University of New York</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,34 +2469,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d07b7c7063ad320</t>
+          <t>https://www.indeed.com/viewjob?jk=c2241815f02a7263</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (IT Infrastructure Engineer 2) - Provisional</t>
+          <t>Engineer, IT AI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>City University of New York</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2504,34 +2504,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Scala, Oracle, Jenkins, Maven, Docker, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2241815f02a7263</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4b0626ba24d7d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Engineer, IT AI</t>
+          <t>​​Sr. Business Intelligence Developer​</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>KLDiscovery</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, Jenkins, Maven, Docker, Jenkins, SonarQube, Git</t>
+          <t>RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, REST API integration, Power BI, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,24 +2549,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4b0626ba24d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e982a157a7d0ccb</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>​​Sr. Business Intelligence Developer​</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KLDiscovery</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, REST API integration, Power BI, Azure DevOps, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,24 +2584,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e982a157a7d0ccb</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f5b97a41606b41</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Salesforce Analyst</t>
+          <t>Software Engineer - Level 2 - Mobility</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Marvin</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Dataflow, Scala, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,24 +2619,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b658acd57044b855</t>
+          <t>https://www.indeed.com/viewjob?jk=4236b2cd8b3fe758</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer III (US)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Oracle, SQL Server, Data Modeling, ETL, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,24 +2654,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f5b97a41606b41</t>
+          <t>https://www.indeed.com/viewjob?jk=99283d35a189051e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - Level 2 - Mobility</t>
+          <t>Junior Data and AI-ML Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Spark, Scala, ETL, ELT, dbt, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2688,146 +2688,6 @@
         </is>
       </c>
       <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4236b2cd8b3fe758</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Engineer III</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=32cddfff9e812a7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Engineer III</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=387517c4b6923e55</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Data Engineer III (US)</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Mount Laurel, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Oracle, SQL Server, Data Modeling, ETL, Python</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99283d35a189051e</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Junior Data and AI-ML Engineer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Lenovo</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Morrisville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Spark, Scala, ETL, ELT, dbt, Power BI, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=29f22521f3c1e203</t>
         </is>

--- a/results/job_matches_2026-10-03.xlsx
+++ b/results/job_matches_2026-10-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,25 +491,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Pipeline Engineer</t>
+          <t>Data Platform Engineer II/III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VedaPointe</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Step Functions, RDS, Azure, Spark, Scala, Spark Streaming, Kafka, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393b88fa8c0cfa99</t>
+          <t>https://www.indeed.com/viewjob?jk=8eeeb83b5522fc44</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II/III</t>
+          <t>Managing Consultant, Palantir Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eeeb83b5522fc44</t>
+          <t>https://www.indeed.com/viewjob?jk=4c403fce849834db</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Solutions Architect (Financial Services)</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SunnyData</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, HDFS, Spark</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69508452f9349a4</t>
+          <t>https://www.indeed.com/viewjob?jk=42cd837866eddbf4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Managing Consultant, Palantir Data &amp; AI Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,14 +624,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c403fce849834db</t>
+          <t>https://www.indeed.com/viewjob?jk=ef02d35010b82b3e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Senior Data Context Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,42 +641,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42cd837866eddbf4</t>
+          <t>https://www.indeed.com/viewjob?jk=2977ae9b1f2b1c97</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>DevOps Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ralph Lauren</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Miami Beach, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,112 +684,112 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef02d35010b82b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=0965aea3b361ff0b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Context Engineer</t>
+          <t>Senior Databricks Migration Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2977ae9b1f2b1c97</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd5a045970f362d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Developer</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ralph Lauren</t>
+          <t>US Neuro LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0965aea3b361ff0b</t>
+          <t>https://www.indeed.com/viewjob?jk=5acff10101632d23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Databricks Migration Engineer</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>TGS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,24 +799,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd5a045970f362d</t>
+          <t>https://www.indeed.com/viewjob?jk=6251b84b65aed773</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Software Engineer III - AWS, Databricks, Python</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>US Neuro LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acff10101632d23</t>
+          <t>https://www.indeed.com/viewjob?jk=54895b1eb093622c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TGS</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6251b84b65aed773</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c7ac7363c390d2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Databricks, Python</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,24 +904,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54895b1eb093622c</t>
+          <t>https://www.indeed.com/viewjob?jk=466d7045497ccea0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Developer - Java, Angular</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, ECS, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,32 +939,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c7ac7363c390d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f75183eedc15fcaa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,32 +974,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=466d7045497ccea0</t>
+          <t>https://www.indeed.com/viewjob?jk=378fe0400293a18c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Java, Angular</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, ECS, RDS, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,24 +1009,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75183eedc15fcaa</t>
+          <t>https://www.indeed.com/viewjob?jk=355669dc3f76e4ef</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Developer Hadoop</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,24 +1044,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378fe0400293a18c</t>
+          <t>https://www.indeed.com/viewjob?jk=17429f6ff7b5e468</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer Hadoop</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,32 +1079,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355669dc3f76e4ef</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4ae8f43eeb5b60</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Developer Hadoop</t>
+          <t>Senior Data Engineer - Indiana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,67 +1114,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17429f6ff7b5e468</t>
+          <t>https://www.indeed.com/viewjob?jk=580c86eee0ba70b4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Developer Hadoop</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4ae8f43eeb5b60</t>
+          <t>https://www.indeed.com/viewjob?jk=4788a8d5c641974d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>AI Engineer Associate Consultant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Inn-Flow Inc.</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, Kimball, ELT</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,32 +1184,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c73622306892de8</t>
+          <t>https://www.indeed.com/viewjob?jk=fb36d41ad52a06bd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Database and Platform Engineer</t>
+          <t>CX Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Builders</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Scala, Databricks Lakehouse, SQL Server, Data Modeling</t>
+          <t>AWS, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,67 +1219,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179abbf1882c12d5</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c2fd229b2485eb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ocala, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33242063b9c39c59</t>
+          <t>https://www.indeed.com/viewjob?jk=3a085e8b62912626</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Indiana</t>
+          <t>Simulation Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, RDS, Azure, Scala, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,67 +1289,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580c86eee0ba70b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b856865fd8381428</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Sentinel Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4788a8d5c641974d</t>
+          <t>https://www.indeed.com/viewjob?jk=e995e33ef6181c97</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Engineer Associate Consultant</t>
+          <t>Senior Guidewire Engineer (PolicyCenter)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,24 +1359,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb36d41ad52a06bd</t>
+          <t>https://www.indeed.com/viewjob?jk=09a5908bdb474bc4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CX Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,24 +1394,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c2fd229b2485eb</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c0b1ce938721b8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - Databricks</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>GA Telesis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,34 +1419,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Cloud Storage, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a085e8b62912626</t>
+          <t>https://www.indeed.com/viewjob?jk=dfd341b35c80136f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Simulation Infrastructure Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,32 +1464,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b856865fd8381428</t>
+          <t>https://www.indeed.com/viewjob?jk=607e2aeb25bf6f87</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Java and Big Data)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sentinel Group</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,32 +1499,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e995e33ef6181c97</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9feb9788d5ad86</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Guidewire Engineer (PolicyCenter)</t>
+          <t>Software Engineer (Java/Big Data)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,102 +1534,102 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a5908bdb474bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8a623c5a6c2d7b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Athena, RDS, Azure, Data Factory, Snowflake, SQL Server, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c0b1ce938721b8</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa8113d5aa47de0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GA Telesis</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Oracle</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfd341b35c80136f</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c7e630377051dd</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, CI/CD, Jenkins, Maven, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,24 +1639,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607e2aeb25bf6f87</t>
+          <t>https://www.indeed.com/viewjob?jk=80ca86983beb5881</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer (Java and Big Data)</t>
+          <t>Data Analytics Specialist Sr</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Lutz, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Cloud Storage, Snowflake, ETL, Power BI, AKS, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,32 +1674,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9feb9788d5ad86</t>
+          <t>https://www.indeed.com/viewjob?jk=6d56b5bcf4b7f491</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer (Java/Big Data)</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,102 +1709,102 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8a623c5a6c2d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0579d402aad195</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, Data Factory, Snowflake, SQL Server, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa8113d5aa47de0</t>
+          <t>https://www.indeed.com/viewjob?jk=e0cc391e05fe7617</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c7e630377051dd</t>
+          <t>https://www.indeed.com/viewjob?jk=26f314384566e0df</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Capitol Tech Solutions Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,32 +1814,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ca86983beb5881</t>
+          <t>https://www.indeed.com/viewjob?jk=89beb9e611e7e10d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Analytics Specialist Sr</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Blood Cancer United</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lutz, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Cloud Storage, Snowflake, ETL, Power BI, AKS, Git</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,24 +1849,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d56b5bcf4b7f491</t>
+          <t>https://www.indeed.com/viewjob?jk=36d95a91a9b838e2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>World View</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, YARN, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,24 +1884,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0579d402aad195</t>
+          <t>https://www.indeed.com/viewjob?jk=17fce9c056aead2f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Engineer</t>
+          <t>Full-stack Engineer 4, Cyber Identity Security</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,24 +1919,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cc391e05fe7617</t>
+          <t>https://www.indeed.com/viewjob?jk=5c73541ffb28ff13</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Full-stack Engineer 4 (Java, Spring Boot, Python, CI/CD)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,24 +1954,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26f314384566e0df</t>
+          <t>https://www.indeed.com/viewjob?jk=cd55268246c76b99</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capitol Tech Solutions Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89beb9e611e7e10d</t>
+          <t>https://www.indeed.com/viewjob?jk=5a68879b2db22f8d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Blood Cancer United</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, Python</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,32 +2024,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d95a91a9b838e2</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b9acf387c2adab</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full-Stack Qlik Sense Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>World View</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Hive, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,67 +2059,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17fce9c056aead2f</t>
+          <t>https://www.indeed.com/viewjob?jk=84a405ff1d454ffa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Cyber Identity Security</t>
+          <t>Senior Associate – Palantir Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c73541ffb28ff13</t>
+          <t>https://www.indeed.com/viewjob?jk=f170b110a592bbc2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Spring Boot, Python, CI/CD)</t>
+          <t>Marketing Data Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hoover Institution, Stanford University</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Stanford, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>EMR, RDS, Medallion Architecture, BigQuery, ELT, dbt, Power BI, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,32 +2129,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd55268246c76b99</t>
+          <t>https://www.indeed.com/viewjob?jk=e021664b78377650</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Trisura</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,24 +2164,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a68879b2db22f8d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb367a6965b10d25</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Trisura Guarantee Insurance Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,24 +2199,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b9acf387c2adab</t>
+          <t>https://www.indeed.com/viewjob?jk=b91959ca412b5c96</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Qlik Sense Engineer</t>
+          <t>Sr Kubernetes Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Hive, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, Git, Python</t>
+          <t>API Gateway, RDS, Vertex AI, Scala, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,24 +2234,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a405ff1d454ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=5de56e58a17ea8ab</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Associate – Palantir Forward Deployed Engineer</t>
+          <t>Site Reliability Engineer (IT Infrastructure Engineer 2) - Provisional</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>City University of New York</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f170b110a592bbc2</t>
+          <t>https://www.indeed.com/viewjob?jk=c2241815f02a7263</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marketing Data Analyst</t>
+          <t>Engineer, IT AI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hoover Institution, Stanford University</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Stanford, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>EMR, RDS, Medallion Architecture, BigQuery, ELT, dbt, Power BI, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, Oracle, Jenkins, Maven, Docker, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,24 +2304,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e021664b78377650</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4b0626ba24d7d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>​​Sr. Business Intelligence Developer​</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Trisura</t>
+          <t>KLDiscovery</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, REST API integration, Power BI, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,24 +2339,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb367a6965b10d25</t>
+          <t>https://www.indeed.com/viewjob?jk=8e982a157a7d0ccb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Trisura Guarantee Insurance Company</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,24 +2374,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b91959ca412b5c96</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f5b97a41606b41</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Kubernetes Platform Engineer</t>
+          <t>Data Engineer III (US)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Vertex AI, Scala, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Oracle, SQL Server, Data Modeling, ETL, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,24 +2409,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5de56e58a17ea8ab</t>
+          <t>https://www.indeed.com/viewjob?jk=99283d35a189051e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer Stf - E4</t>
+          <t>Junior Data and AI-ML Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,260 +2434,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Databricks, Spark, Scala, ETL, ELT, dbt, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d07b7c7063ad320</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer (IT Infrastructure Engineer 2) - Provisional</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>City University of New York</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2241815f02a7263</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Engineer, IT AI</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, Jenkins, Maven, Docker, Jenkins, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4b0626ba24d7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>​​Sr. Business Intelligence Developer​</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>KLDiscovery</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, REST API integration, Power BI, Azure DevOps, Python</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e982a157a7d0ccb</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>C.H. Robinson</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f5b97a41606b41</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Software Engineer - Level 2 - Mobility</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Cintas</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Mason, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4236b2cd8b3fe758</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Data Engineer III (US)</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Mount Laurel, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Oracle, SQL Server, Data Modeling, ETL, Python</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99283d35a189051e</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Junior Data and AI-ML Engineer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Lenovo</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Morrisville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Spark, Scala, ETL, ELT, dbt, Power BI, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=29f22521f3c1e203</t>
         </is>

--- a/results/job_matches_2026-10-03.xlsx
+++ b/results/job_matches_2026-10-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,25 +701,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Databricks Migration Engineer</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>US Neuro LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,24 +729,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd5a045970f362d</t>
+          <t>https://www.indeed.com/viewjob?jk=5acff10101632d23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>US Neuro LLC</t>
+          <t>TGS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,24 +764,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acff10101632d23</t>
+          <t>https://www.indeed.com/viewjob?jk=6251b84b65aed773</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>API &amp; Data Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TGS</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -789,17 +789,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6251b84b65aed773</t>
+          <t>https://www.indeed.com/viewjob?jk=a3babb1e30d3465d</t>
         </is>
       </c>
     </row>
@@ -981,17 +981,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer Hadoop</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355669dc3f76e4ef</t>
+          <t>https://www.indeed.com/viewjob?jk=17429f6ff7b5e468</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1044,32 +1044,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17429f6ff7b5e468</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4ae8f43eeb5b60</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Developer Hadoop</t>
+          <t>AI Engineer Associate Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,102 +1079,102 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4ae8f43eeb5b60</t>
+          <t>https://www.indeed.com/viewjob?jk=fb36d41ad52a06bd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Indiana</t>
+          <t>Sr Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580c86eee0ba70b4</t>
+          <t>https://www.indeed.com/viewjob?jk=3a085e8b62912626</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Simulation Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4788a8d5c641974d</t>
+          <t>https://www.indeed.com/viewjob?jk=b856865fd8381428</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Engineer Associate Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Sentinel Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb36d41ad52a06bd</t>
+          <t>https://www.indeed.com/viewjob?jk=e995e33ef6181c97</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CX Machine Learning Engineer</t>
+          <t>Senior Guidewire Engineer (PolicyCenter)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,24 +1219,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c2fd229b2485eb</t>
+          <t>https://www.indeed.com/viewjob?jk=09a5908bdb474bc4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - Databricks</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,34 +1244,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a085e8b62912626</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c0b1ce938721b8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Simulation Infrastructure Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b856865fd8381428</t>
+          <t>https://www.indeed.com/viewjob?jk=607e2aeb25bf6f87</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sentinel Group</t>
+          <t>GA Telesis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,32 +1324,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e995e33ef6181c97</t>
+          <t>https://www.indeed.com/viewjob?jk=dfd341b35c80136f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Guidewire Engineer (PolicyCenter)</t>
+          <t>Software Engineer (Java and Big Data)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,32 +1359,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a5908bdb474bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9feb9788d5ad86</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer (Java/Big Data)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,67 +1394,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c0b1ce938721b8</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8a623c5a6c2d7b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GA Telesis</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Oracle</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfd341b35c80136f</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c7e630377051dd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Government and Infrastructure - Cybersecurity - DevSecOps Senior Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, CI/CD, Jenkins, Maven, Docker</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,24 +1464,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607e2aeb25bf6f87</t>
+          <t>https://www.indeed.com/viewjob?jk=8204bb14afee5287</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer (Java and Big Data)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,24 +1499,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9feb9788d5ad86</t>
+          <t>https://www.indeed.com/viewjob?jk=80ca86983beb5881</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer (Java/Big Data)</t>
+          <t>Government and Infrastructure - Cybersecurity - DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,102 +1534,102 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8a623c5a6c2d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=4f386708dcb9013c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, Data Factory, Snowflake, SQL Server, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa8113d5aa47de0</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0579d402aad195</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c7e630377051dd</t>
+          <t>https://www.indeed.com/viewjob?jk=e0cc391e05fe7617</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,32 +1639,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ca86983beb5881</t>
+          <t>https://www.indeed.com/viewjob?jk=26f314384566e0df</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Analytics Specialist Sr</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Capitol Tech Solutions Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lutz, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Cloud Storage, Snowflake, ETL, Power BI, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,24 +1674,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d56b5bcf4b7f491</t>
+          <t>https://www.indeed.com/viewjob?jk=89beb9e611e7e10d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Blood Cancer United</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,24 +1709,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0579d402aad195</t>
+          <t>https://www.indeed.com/viewjob?jk=36d95a91a9b838e2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>World View</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, YARN, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,24 +1744,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cc391e05fe7617</t>
+          <t>https://www.indeed.com/viewjob?jk=17fce9c056aead2f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Full-stack Engineer 4, Cyber Identity Security</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,24 +1779,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26f314384566e0df</t>
+          <t>https://www.indeed.com/viewjob?jk=5c73541ffb28ff13</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4 (Java, Spring Boot, Python, CI/CD)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capitol Tech Solutions Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,24 +1814,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89beb9e611e7e10d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd55268246c76b99</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blood Cancer United</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,32 +1849,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d95a91a9b838e2</t>
+          <t>https://www.indeed.com/viewjob?jk=5a68879b2db22f8d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>World View</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, Python</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,32 +1884,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17fce9c056aead2f</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b9acf387c2adab</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Cyber Identity Security</t>
+          <t>Senior Full-Stack Qlik Sense Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Hive, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,67 +1919,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c73541ffb28ff13</t>
+          <t>https://www.indeed.com/viewjob?jk=84a405ff1d454ffa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Spring Boot, Python, CI/CD)</t>
+          <t>Senior Associate – Palantir Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd55268246c76b99</t>
+          <t>https://www.indeed.com/viewjob?jk=f170b110a592bbc2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Marketing Data Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hoover Institution, Stanford University</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Stanford, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>EMR, RDS, Medallion Architecture, BigQuery, ELT, dbt, Power BI, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,24 +1989,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a68879b2db22f8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e021664b78377650</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Trisura</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,24 +2024,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b9acf387c2adab</t>
+          <t>https://www.indeed.com/viewjob?jk=fb367a6965b10d25</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Qlik Sense Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Trisura Guarantee Insurance Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Hive, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a405ff1d454ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=b91959ca412b5c96</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Associate – Palantir Forward Deployed Engineer</t>
+          <t>Site Reliability Engineer (IT Infrastructure Engineer 2) - Provisional</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>City University of New York</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,24 +2094,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f170b110a592bbc2</t>
+          <t>https://www.indeed.com/viewjob?jk=c2241815f02a7263</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Marketing Data Analyst</t>
+          <t>Engineer, IT AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hoover Institution, Stanford University</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Stanford, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>EMR, RDS, Medallion Architecture, BigQuery, ELT, dbt, Power BI, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, Oracle, Jenkins, Maven, Docker, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e021664b78377650</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4b0626ba24d7d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>​​Sr. Business Intelligence Developer​</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Trisura</t>
+          <t>KLDiscovery</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, REST API integration, Power BI, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,24 +2164,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb367a6965b10d25</t>
+          <t>https://www.indeed.com/viewjob?jk=8e982a157a7d0ccb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Engineer III (US)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Trisura Guarantee Insurance Company</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Oracle, SQL Server, Data Modeling, ETL, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,252 +2199,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b91959ca412b5c96</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Sr Kubernetes Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Vertex AI, Scala, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5de56e58a17ea8ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer (IT Infrastructure Engineer 2) - Provisional</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>City University of New York</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2241815f02a7263</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Engineer, IT AI</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, Jenkins, Maven, Docker, Jenkins, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4b0626ba24d7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>​​Sr. Business Intelligence Developer​</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>KLDiscovery</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, REST API integration, Power BI, Azure DevOps, Python</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e982a157a7d0ccb</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>C.H. Robinson</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f5b97a41606b41</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Data Engineer III (US)</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Mount Laurel, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Oracle, SQL Server, Data Modeling, ETL, Python</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=99283d35a189051e</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Junior Data and AI-ML Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Lenovo</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Morrisville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Spark, Scala, ETL, ELT, dbt, Power BI, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29f22521f3c1e203</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-03.xlsx
+++ b/results/job_matches_2026-10-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,17 +526,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Managing Consultant, Palantir Data &amp; AI Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -544,7 +544,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,14 +554,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c403fce849834db</t>
+          <t>https://www.indeed.com/viewjob?jk=42cd837866eddbf4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -571,15 +571,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>Miami Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42cd837866eddbf4</t>
+          <t>https://www.indeed.com/viewjob?jk=ef02d35010b82b3e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>US Neuro LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Miami Beach, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,94 +624,94 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef02d35010b82b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=5acff10101632d23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Context Engineer</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TGS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2977ae9b1f2b1c97</t>
+          <t>https://www.indeed.com/viewjob?jk=6251b84b65aed773</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Developer</t>
+          <t>API &amp; Data Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ralph Lauren</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0965aea3b361ff0b</t>
+          <t>https://www.indeed.com/viewjob?jk=a3babb1e30d3465d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Software Engineer III - AWS, Databricks, Python</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>US Neuro LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acff10101632d23</t>
+          <t>https://www.indeed.com/viewjob?jk=54895b1eb093622c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TGS</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,67 +764,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6251b84b65aed773</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c7ac7363c390d2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>API &amp; Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3babb1e30d3465d</t>
+          <t>https://www.indeed.com/viewjob?jk=466d7045497ccea0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Databricks, Python</t>
+          <t>Senior Full Stack Developer - Java, Angular</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, ECS, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54895b1eb093622c</t>
+          <t>https://www.indeed.com/viewjob?jk=f75183eedc15fcaa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer Hadoop</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c7ac7363c390d2</t>
+          <t>https://www.indeed.com/viewjob?jk=17429f6ff7b5e468</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer Hadoop</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=466d7045497ccea0</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4ae8f43eeb5b60</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Java, Angular</t>
+          <t>AI Engineer Associate Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, ECS, RDS, Spark, Scala</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,67 +939,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75183eedc15fcaa</t>
+          <t>https://www.indeed.com/viewjob?jk=fb36d41ad52a06bd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Sr Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378fe0400293a18c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a085e8b62912626</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Developer Hadoop</t>
+          <t>Simulation Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,32 +1009,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17429f6ff7b5e468</t>
+          <t>https://www.indeed.com/viewjob?jk=b856865fd8381428</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Developer Hadoop</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Sentinel Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,32 +1044,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4ae8f43eeb5b60</t>
+          <t>https://www.indeed.com/viewjob?jk=e995e33ef6181c97</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer Associate Consultant</t>
+          <t>Senior Guidewire Engineer (PolicyCenter)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,24 +1079,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb36d41ad52a06bd</t>
+          <t>https://www.indeed.com/viewjob?jk=09a5908bdb474bc4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - Databricks</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1104,34 +1104,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a085e8b62912626</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c0b1ce938721b8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Simulation Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>GA Telesis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,32 +1149,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b856865fd8381428</t>
+          <t>https://www.indeed.com/viewjob?jk=dfd341b35c80136f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Java and Big Data)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sentinel Group</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,32 +1184,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e995e33ef6181c97</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9feb9788d5ad86</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Guidewire Engineer (PolicyCenter)</t>
+          <t>Software Engineer (Java/Big Data)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,67 +1219,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a5908bdb474bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8a623c5a6c2d7b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c0b1ce938721b8</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c7e630377051dd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Government and Infrastructure - Cybersecurity - DevSecOps Senior Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, CI/CD, Jenkins, Maven, Docker</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,32 +1289,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607e2aeb25bf6f87</t>
+          <t>https://www.indeed.com/viewjob?jk=8204bb14afee5287</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Government and Infrastructure - Cybersecurity - DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GA Telesis</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Oracle</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,32 +1324,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfd341b35c80136f</t>
+          <t>https://www.indeed.com/viewjob?jk=4f386708dcb9013c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer (Java and Big Data)</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,32 +1359,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9feb9788d5ad86</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0579d402aad195</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer (Java/Big Data)</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,67 +1394,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8a623c5a6c2d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=26f314384566e0df</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Capitol Tech Solutions Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c7e630377051dd</t>
+          <t>https://www.indeed.com/viewjob?jk=89beb9e611e7e10d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Government and Infrastructure - Cybersecurity - DevSecOps Senior Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>World View</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, YARN, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,32 +1464,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8204bb14afee5287</t>
+          <t>https://www.indeed.com/viewjob?jk=17fce9c056aead2f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Full-stack Engineer 4, Cyber Identity Security</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,19 +1499,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ca86983beb5881</t>
+          <t>https://www.indeed.com/viewjob?jk=5c73541ffb28ff13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Government and Infrastructure - Cybersecurity - DevSecOps Engineer</t>
+          <t>Full-stack Engineer 4 (Java, Spring Boot, Python, CI/CD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1520,11 +1520,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f386708dcb9013c</t>
+          <t>https://www.indeed.com/viewjob?jk=cd55268246c76b99</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1569,32 +1569,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0579d402aad195</t>
+          <t>https://www.indeed.com/viewjob?jk=5a68879b2db22f8d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, Python</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,67 +1604,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cc391e05fe7617</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b9acf387c2adab</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Associate – Palantir Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26f314384566e0df</t>
+          <t>https://www.indeed.com/viewjob?jk=f170b110a592bbc2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Marketing Data Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capitol Tech Solutions Inc</t>
+          <t>Hoover Institution, Stanford University</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Stanford, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>EMR, RDS, Medallion Architecture, BigQuery, ELT, dbt, Power BI, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,67 +1674,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89beb9e611e7e10d</t>
+          <t>https://www.indeed.com/viewjob?jk=e021664b78377650</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer (IT Infrastructure Engineer 2) - Provisional</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Blood Cancer United</t>
+          <t>City University of New York</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
+          <t>RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d95a91a9b838e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c2241815f02a7263</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer, IT AI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>World View</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, Jenkins, Maven, Docker, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,32 +1744,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17fce9c056aead2f</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4b0626ba24d7d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Cyber Identity Security</t>
+          <t>Data Engineer III (US)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Oracle, SQL Server, Data Modeling, ETL, Python</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1778,426 +1778,6 @@
         </is>
       </c>
       <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c73541ffb28ff13</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Java, Spring Boot, Python, CI/CD)</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd55268246c76b99</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a68879b2db22f8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Netsmart Technologies</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, Python</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b9acf387c2adab</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Senior Full-Stack Qlik Sense Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Bloomberg</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>RDS, Hive, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84a405ff1d454ffa</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Senior Associate – Palantir Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Fannie Mae</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f170b110a592bbc2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Marketing Data Analyst</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Hoover Institution, Stanford University</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Stanford, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>EMR, RDS, Medallion Architecture, BigQuery, ELT, dbt, Power BI, Tableau, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e021664b78377650</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Senior Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Trisura</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb367a6965b10d25</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Senior Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Trisura Guarantee Insurance Company</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b91959ca412b5c96</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer (IT Infrastructure Engineer 2) - Provisional</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>City University of New York</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2241815f02a7263</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Engineer, IT AI</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, Jenkins, Maven, Docker, Jenkins, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4b0626ba24d7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>​​Sr. Business Intelligence Developer​</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>KLDiscovery</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, REST API integration, Power BI, Azure DevOps, Python</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e982a157a7d0ccb</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Data Engineer III (US)</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Mount Laurel, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Oracle, SQL Server, Data Modeling, ETL, Python</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=99283d35a189051e</t>
         </is>
